--- a/CodeDo_Editor_capacity_with_visual_explanations.xlsx
+++ b/CodeDo_Editor_capacity_with_visual_explanations.xlsx
@@ -5717,22 +5717,22 @@
       </c>
       <c r="C217" s="6" t="inlineStr">
         <is>
-          <t>Conceptual only</t>
+          <t>Built (verified)</t>
         </is>
       </c>
       <c r="D217" s="4" t="inlineStr">
         <is>
-          <t>Best-practice guidance, not a testable behavior</t>
+          <t>Initially misclassified as conceptual-only; the lesson's shipped data has real writeRun/debug stages using GlobalScope.launch, withContext, and CoroutineDispatcher. Built and execution-verified: GlobalScope.launch (deliberately unregistered with any scope, so its action never runs synchronously -- reproducing the real detached-work anti-pattern honestly) plus withContext/dispatcher-aware launch are runnable and verified against every Learn/Explore/Predict/Write&amp;Run/Debug snippet (scripts/audit-world16-quality.ts, world16CoroutineLessons.test.ts) plus the full regression suite, zero regressions. See PITFALLS.md.</t>
         </is>
       </c>
       <c r="E217" s="12" t="inlineStr">
         <is>
-          <t>Not Runnable</t>
+          <t>Runnable</t>
         </is>
       </c>
       <c r="G217" s="18" t="inlineStr">
         <is>
-          <t>Not needed — text and code examples are sufficient</t>
+          <t>Animated scope-ownership diagram -- GlobalScope leak vs structured coroutineScope fix</t>
         </is>
       </c>
     </row>
